--- a/donnees/halden_base.xlsx
+++ b/donnees/halden_base.xlsx
@@ -29,17 +29,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal_Audit" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parametres'!$A$1:$C$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pack_Pays'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Grille_Decision'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parametres'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pack_Pays'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Grille_Decision'!$A$1:$N$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Projets'!$A$1:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Jalons'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unites'!$A$1:$J$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Acheteurs'!$A$1:$J$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Acheteurs'!$A$1:$K$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Contrats'!$A$1:$H$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Echeancier'!$A$1:$N$165</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Relances'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Messages_Entrants'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Messages_Entrants'!$A$1:$J$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Leads'!$A$1:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Reserves'!$A$1:$K$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Sous_Traitants'!$A$1:$D$7</definedName>
@@ -673,7 +673,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>• Jalons : passez un jalon en CERTIFIÉ avec une date → l'agent Collections prépare les appels de fonds.</t>
+          <t>• Jalons : passez un jalon en CERTIFIÉ avec une date → l'agent Encaissements prépare les appels de fonds.</t>
         </is>
       </c>
       <c r="C20" s="1" t="n"/>
@@ -682,7 +682,7 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>• Grille_Decision : changez les notes V/C → le niveau d'autonomie de l'agent change au prochain cycle.</t>
+          <t>• Grille_Decision : changez les notes V/C → le niveau change, sans jamais passer sous le plancher du code.</t>
         </is>
       </c>
       <c r="C21" s="1" t="n"/>
@@ -732,7 +732,7 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>• Journal_Audit : chaque action, chaînée par hash (toute modification a posteriori se voit).</t>
+          <t>• Journal_Audit : chaque action, chaînée et signée (HMAC) : toute modification ou coupure se voit.</t>
         </is>
       </c>
       <c r="C27" s="1" t="n"/>
@@ -753,7 +753,11 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Règle du pilote : chaque message vers un acheteur est validé par un humain (écrite dans le code).</t>
+        </is>
+      </c>
       <c r="C30" s="1" t="n"/>
     </row>
     <row r="31">
@@ -10438,7 +10442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10451,6 +10455,9 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -10502,6 +10509,21 @@
       <c r="J1" s="6" t="inlineStr">
         <is>
           <t>methode</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>sens</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>acheteur_candidat</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>empreinte</t>
         </is>
       </c>
     </row>
@@ -10699,17 +10721,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -10735,22 +10759,32 @@
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
+          <t>expediteur</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
           <t>texte</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>statut</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>categorie</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>langue_detectee</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>signaux</t>
         </is>
       </c>
     </row>
@@ -10773,18 +10807,24 @@
           <t>email</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>priya.raman@mail.example</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Hello, could you tell me when my next payment is due and how much it is?</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>NOUVEAU</t>
         </is>
       </c>
-      <c r="G2" s="7" t="n"/>
       <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -10805,18 +10845,24 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>+971 50 902 9975</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>متى موعد التسليم المتوقع للمشروع؟</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>NOUVEAU</t>
         </is>
       </c>
-      <c r="G3" s="7" t="n"/>
       <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -10837,18 +10883,24 @@
           <t>email</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>daniel.oconnor@mail.example</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Hi, I would like to change the kitchen finish to dark oak instead of the white gloss. Is it possible?</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>NOUVEAU</t>
         </is>
       </c>
-      <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -10869,18 +10921,24 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>+971 50 753 2250</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>I lost my job last month. Can I postpone my next payment by 3 months? I really want to keep the apartment.</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>NOUVEAU</t>
         </is>
       </c>
-      <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -10901,18 +10959,24 @@
           <t>email</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>yuki.tanaka@mail.example</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>I want to cancel my purchase and get a refund of everything I paid. Please process it.</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>NOUVEAU</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -10933,18 +10997,24 @@
           <t>email</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>sophie.marchand@mail.example</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Bonjour, pouvez-vous m'envoyer mon relevé de compte (statement) à jour ? Merci.</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>NOUVEAU</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -10965,21 +11035,179 @@
           <t>email</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>lukas.becker@mail.example</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Any construction update? Last photos were from September.</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>NOUVEAU</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>MSG-0008</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>ACH-007</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>+971 50 869 8226</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>دفعت القسط أمس، لماذا التذكير؟</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>MSG-0009</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>ACH-011</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>aisha.al.suwaidi@mail.example</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>What is my balance?</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>MSG-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>ACH-004</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>+971 50 328 7891</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Please cancel the reminders, I'm talking to my lawyer.</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>MSG-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>ACH-001</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>+971 55 000 1122</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Hi, I'm Omar's assistant, send me his statement please.</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:J12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12267,7 +12495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12375,8 +12603,59 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>perimetre</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>PILOTE</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>PILOTE = encaissements seuls (Dubaï) | VISION = les six agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>approbateurs_autorises</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Sara K. · CFO</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Seules ces personnes peuvent décider (séparées par ;). Connexion réelle à prévoir avant le pilote</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>regle_approbation</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Chaque message vers un acheteur est validé par un humain</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Écrite dans le code (garde-fous), affichée ici pour mémoire : non modifiable dans l'Excel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:C9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12473,7 +12752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12655,45 +12934,43 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>delai_signature_spa_jours</t>
+          <t>tolerance_frais_bancaires_aed</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>jours</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Pratique de marché</t>
+          <t>Choix Halden : écart toléré pour frais bancaires (toujours validé)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>À VÉRIFIER</t>
+          <t>HYPOTHÈSE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>delai_enregistrement_oqood_jours</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>jours</t>
-        </is>
-      </c>
+          <t>defaut_notification_dld</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Le promoteur notifie le défaut à la DLD, qui notifie l'acheteur (loi de Dubaï n° 13/2008, art. 11, modifiée par la loi n° 19/2017)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>DLD / Oqood</t>
+          <t>Loi 13/2008 art. 11 ; Al Tamimi</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -12705,20 +12982,20 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>frais_oqood_pct</t>
+          <t>defaut_delai_dld_jours</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>% du prix</t>
+          <t>jours</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>DLD (frais de transfert)</t>
+          <t>Loi 13/2008 art. 11 modifiée</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -12730,20 +13007,18 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>garantie_finitions_mois</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>mois</t>
-        </is>
-      </c>
+          <t>defaut_option_80_plus</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>maintenir le contrat et réclamer le solde, ou demander la vente du lot aux enchères via la DLD, ou résilier en conservant au plus 40 % du prix</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Pratique contractuelle (DLP)</t>
+          <t>Loi 19/2017</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -12755,20 +13030,18 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>garantie_structure_ans</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>ans</t>
-        </is>
-      </c>
+          <t>defaut_option_60_80</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>résilier en conservant au plus 40 % du prix</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Code civil EAU (responsabilité décennale)</t>
+          <t>Loi 19/2017</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -12780,41 +13053,43 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>penalites_retard</t>
+          <t>defaut_option_moins_60</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Selon clause SPA</t>
+          <t>résilier en conservant au plus 25 % du prix</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Jamais calculées par l'IA</t>
+          <t>Loi 19/2017</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>RÈGLE HALDEN</t>
+          <t>À VÉRIFIER</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>compte_escrow</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Obligatoire</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr"/>
+          <t>delai_signature_spa_jours</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>jours</t>
+        </is>
+      </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Loi Dubaï n°8/2007 (comptes escrow)</t>
+          <t>Pratique de marché</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -12826,24 +13101,170 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>delai_enregistrement_oqood_jours</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>jours</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>DLD / Oqood</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>À VÉRIFIER</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>frais_oqood_pct</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>% du prix</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>DLD (frais de transfert)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>À VÉRIFIER</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>garantie_finitions_mois</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>mois</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Pratique contractuelle (DLP)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>À VÉRIFIER</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>garantie_structure_ans</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>ans</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Code civil EAU (responsabilité décennale)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>À VÉRIFIER</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>penalites_retard</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Selon clause SPA</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Jamais calculées par l'IA</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>RÈGLE HALDEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>compte_escrow</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Obligatoire</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Loi Dubaï n°8/2007 (comptes escrow)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>À VÉRIFIER</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>langues</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>EN, AR</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>FAIT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12855,7 +13276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12871,6 +13292,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -12939,6 +13361,11 @@
           <t>exemple</t>
         </is>
       </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>sensibilite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -12953,7 +13380,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Collections</t>
+          <t>Encaissements</t>
         </is>
       </c>
       <c r="D2" s="7" t="n">
@@ -12969,7 +13396,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>1</v>
@@ -12979,7 +13406,7 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>AUTONOME</t>
+          <t>VALIDATION</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -12990,6 +13417,11 @@
       <c r="M2" s="9" t="inlineStr">
         <is>
           <t>Rappel courtois 3 jours après l'échéance</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>C1−1 → RÈGLE</t>
         </is>
       </c>
     </row>
@@ -13045,6 +13477,11 @@
           <t>Encaissé, en retard, file d'attente</t>
         </is>
       </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>C1−1 → RÈGLE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -13098,6 +13535,11 @@
           <t>Fuite sous évier → plombier, 48 h</t>
         </is>
       </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>C1−1 → RÈGLE ; C2+1 → VALIDATION</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -13128,7 +13570,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>2</v>
@@ -13138,7 +13580,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>AUTONOME</t>
+          <t>VALIDATION</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -13149,6 +13591,11 @@
       <c r="M5" s="9" t="inlineStr">
         <is>
           <t>« Quand est ma prochaine échéance ? »</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>stable à ±1</t>
         </is>
       </c>
     </row>
@@ -13165,7 +13612,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Collections</t>
+          <t>Encaissements</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
@@ -13204,6 +13651,11 @@
           <t>Jalon 40 % certifié → 20 appels</t>
         </is>
       </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>C1−1 → RÈGLE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -13218,7 +13670,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Collections</t>
+          <t>Encaissements</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
@@ -13257,6 +13709,11 @@
           <t>Virement sans référence</t>
         </is>
       </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>stable à ±1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -13310,6 +13767,11 @@
           <t>Lettre d'avancement avec photos</t>
         </is>
       </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>V1−1 → AUCUN AGENT ; C1−1 → RÈGLE ; C2−1 → AUTONOME</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -13363,6 +13825,11 @@
           <t>Changer la finition de la cuisine</t>
         </is>
       </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>V1−1 → AUCUN AGENT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -13416,6 +13883,11 @@
           <t>Proposer le lot adapté au budget</t>
         </is>
       </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>C2−1 → AUTONOME</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -13469,6 +13941,11 @@
           <t>10 % du prix au jalon 40 %</t>
         </is>
       </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>C1+1 → VALIDATION</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -13522,6 +13999,11 @@
           <t>Finitions 12 mois, structure 10 ans</t>
         </is>
       </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>V1−1 → AUCUN AGENT ; C1+1 → VALIDATION</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -13536,7 +14018,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Collections</t>
+          <t>Encaissements</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
@@ -13575,6 +14057,11 @@
           <t>Report demandé après perte d'emploi</t>
         </is>
       </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>V1−1 → AUCUN AGENT ; C2−1 → VALIDATION ; C4−1 → VALIDATION</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -13628,6 +14115,11 @@
           <t>Signature, résiliation, remboursement</t>
         </is>
       </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>C2−1 → VALIDATION ; C4−1 → VALIDATION</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -13681,6 +14173,11 @@
           <t>Fissure + menace d'avocat</t>
         </is>
       </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>V1−1 → AUCUN AGENT ; C2−1 → VALIDATION ; C4−1 → VALIDATION</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -13690,12 +14187,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Lettrage exact (référence + montant)</t>
+          <t>Lettrage exact (référence + payeur + montant)</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Collections</t>
+          <t>Encaissements</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -13734,6 +14231,11 @@
           <t>HLD-ACR-0304-04 = montant dû</t>
         </is>
       </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>C1+1 → VALIDATION</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -13764,7 +14266,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>2</v>
@@ -13774,7 +14276,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>AUTONOME</t>
+          <t>VALIDATION</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -13785,6 +14287,11 @@
       <c r="M17" s="9" t="inlineStr">
         <is>
           <t>Demander la copie du passeport</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>C1−1 → RÈGLE ; C2−1 → AUTONOME</t>
         </is>
       </c>
     </row>
@@ -13840,6 +14347,11 @@
           <t>SPA non signé après 30 jours</t>
         </is>
       </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>C1−1 → RÈGLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -13870,7 +14382,7 @@
         <v>2</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>1</v>
@@ -13880,7 +14392,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>AUTONOME</t>
+          <t>VALIDATION</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -13893,9 +14405,14 @@
           <t>Accusé + intervention planifiée</t>
         </is>
       </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>V1−1 → AUCUN AGENT ; C1−1 → RÈGLE ; C2−1 → AUTONOME</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:N19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15804,7 +16321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -15817,6 +16334,7 @@
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -15870,6 +16388,11 @@
           <t>kyc_justif_adresse</t>
         </is>
       </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>contact_auto</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -15922,6 +16445,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -15974,6 +16502,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -16026,6 +16559,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -16078,6 +16616,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -16130,6 +16673,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -16182,6 +16730,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -16234,6 +16787,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -16286,6 +16844,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -16338,6 +16901,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -16390,6 +16958,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -16442,6 +17015,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -16494,6 +17072,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -16546,6 +17129,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -16598,6 +17186,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -16650,6 +17243,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -16702,6 +17300,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -16754,6 +17357,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -16806,6 +17414,11 @@
           <t>MANQUANT</t>
         </is>
       </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -16858,6 +17471,11 @@
           <t>MANQUANT</t>
         </is>
       </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -16910,6 +17528,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -16962,6 +17585,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -17014,6 +17642,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -17066,6 +17699,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -17118,6 +17756,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -17170,6 +17813,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -17222,6 +17870,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -17274,6 +17927,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -17326,6 +17984,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -17378,6 +18041,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -17430,6 +18098,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -17482,6 +18155,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -17534,9 +18212,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J33"/>
+  <autoFilter ref="A1:K33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
